--- a/PPG/Agendas de Pesquisa.xlsx
+++ b/PPG/Agendas de Pesquisa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8059D588-B17D-7240-83E5-21B8AA837AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCAC90C-7DBF-D54B-9908-D5558D448CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="1000" windowWidth="27160" windowHeight="16400" xr2:uid="{D63A89C5-1CF9-944C-B99E-829D01D159A4}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Documento</t>
   </si>
@@ -119,6 +119,18 @@
   </si>
   <si>
     <t>Coordenação de Aperfeiçoamento de Pessoal de Nível Superior</t>
+  </si>
+  <si>
+    <t>2024-2034</t>
+  </si>
+  <si>
+    <t>Estratégia Nacional de Ciência, Tecnologia e Inovação 2024-2034</t>
+  </si>
+  <si>
+    <t>Ministério da Ciência, Tecnologia e Inovação</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/mcti/pt-br/centrais-de-conteudo/publicacoes-mcti/encti/encti-2024-2034.pdf</t>
   </si>
 </sst>
 </file>
@@ -490,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57483A5-AD19-4044-AC8A-937A31BA4E28}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.83203125" bestFit="1" customWidth="1"/>
@@ -596,6 +608,20 @@
         <v>26</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{A32B3E1A-44E1-154A-911E-37E2C2699DDA}"/>
@@ -604,6 +630,7 @@
     <hyperlink ref="D3" r:id="rId4" xr:uid="{996EBDA4-A466-F74F-9E53-063040DAE49D}"/>
     <hyperlink ref="D6" r:id="rId5" xr:uid="{37E04941-0EDB-6D46-A50D-3C3A55C0F462}"/>
     <hyperlink ref="D7" r:id="rId6" xr:uid="{1271E09A-CE50-7044-9AC8-ACBABDC0D5C2}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{5790F53A-EB0D-BB42-82CE-818AAB71C344}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
